--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -505,6 +505,34 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>knipex pliers set mini</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>$80.37</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>73.7%</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -533,6 +533,34 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>makeup travel organizer with wheels</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="n">
+        <v>53</v>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>$122.34</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52.8%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -561,6 +561,34 @@
         </is>
       </c>
     </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>shoe rack bench with storage</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>$84.47</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>78.6%</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -589,6 +589,34 @@
         </is>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>arch trellis for climbing plants outdoor</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>$45.55</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>70.8%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -617,6 +617,34 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>pgytech camera bag 22l</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>$104.14</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -645,6 +645,34 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>ipl hair removal device</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>$196.13</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>92.9%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -673,6 +673,34 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>cedar raised garden bed with legs</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>$74.35</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>61.4%</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -701,6 +701,34 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>raised garden bed with trellis and hanging roof</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>$67.23</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>57.4%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F10"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -729,6 +729,34 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>raised bed trellis arch</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>$44.21</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>53.4%</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -757,6 +757,34 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>shakti acupressure mat level 1</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>$54.54</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -785,6 +785,34 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>infant pulse oximeter newborn medical grade</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>$58.32</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -813,6 +813,34 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>beaba baby food maker stainless steel</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>$101.01</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -841,6 +841,34 @@
         </is>
       </c>
     </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>curved reflector photography</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>$75.51</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>57.9%</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -869,6 +869,34 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>cleaning caddy on wheels heavy duty</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>$91.65</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>95.2%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F16"/>
+  <dimension ref="A1:F17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -897,6 +897,34 @@
         </is>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ego lawn edger with battery</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>$141.66</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -925,6 +925,34 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>led headlamp assembly</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>$144.86</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>84.6%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F18"/>
+  <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -953,6 +953,34 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>pgytech camera bag</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>$131.74</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -981,6 +981,34 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>trellis arch</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>$45.74</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>31</v>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>64.6%</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1009,6 +1009,34 @@
         </is>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>monitor arm white</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>$49.79</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>65.0%</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1037,6 +1037,34 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>gym mats for home workout 1 inch</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>$58.45</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1065,6 +1065,34 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>outdoor cooking station</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>$105.65</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F23"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1093,6 +1093,34 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>backdrop stand 10x10 flat base</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>$86.63</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1121,6 +1121,34 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>battery grip for canon r6 mark ii</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>$108.20</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>86.7%</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1149,6 +1149,34 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>surf fishing rod holder hitch</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>$60.31</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>26</v>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>43.3%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1177,6 +1177,34 @@
         </is>
       </c>
     </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>first aid kit for car with tourniquet</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>$52.73</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1205,6 +1205,34 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>outdoor planters for porch rectangle</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>$96.82</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F28"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1233,6 +1233,34 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>rolling cleaning caddy with wheels and detachable trolley</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>$70.77</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>70.2%</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:F30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1261,6 +1261,34 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>ups battery backup &amp; surge protector pure sine wave</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>$176.50</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1289,6 +1289,34 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>fishing rod holder for car roof top outside</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>$40.47</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1317,6 +1317,34 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>ego lawn edgers battery powered</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>$125.41</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F32"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1345,6 +1345,34 @@
         </is>
       </c>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>lawn edgers battery powered dewalt and blower</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>$97.06</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>95.0%</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1373,6 +1373,34 @@
         </is>
       </c>
     </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>seiko metronome standard line monotone smw006a watch</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>$40.35</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1401,6 +1401,34 @@
         </is>
       </c>
     </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>dewalt tool bag</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>$50.60</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1429,6 +1429,34 @@
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>lawn edger cordless ego</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>$135.60</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>87.5%</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1457,6 +1457,34 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>hammock chair with stand included</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>$93.93</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>41</v>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>73.2%</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F37"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1485,6 +1485,34 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>makeup storage organizer cart</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>$46.26</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>45.8%</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1513,6 +1513,34 @@
         </is>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>arched garden trellis for climbing plants</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>$46.88</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>73.3%</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1541,6 +1541,34 @@
         </is>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>tuner for truck super chip</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>$307.58</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1569,6 +1569,34 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>charging station for nightstand wood</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>$36.29</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F41"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1597,6 +1597,34 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>trellis arch with planters</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>$59.30</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>92.9%</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1625,6 +1625,34 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>leki trekking poles</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>$117.09</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1653,6 +1653,34 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>garden cart wheels 16 inch</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>$52.69</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>24</v>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>53.3%</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1681,6 +1681,34 @@
         </is>
       </c>
     </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>drill bit set for metal</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>$55.02</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F45"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1709,6 +1709,34 @@
         </is>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>backdrop stand for parties arch</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>$46.83</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1737,6 +1737,34 @@
         </is>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>fishing rod holder for truck hitch</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>$53.53</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1765,6 +1765,34 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>hieha portable car jump starter with air compressor</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>$52.79</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>53.8%</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1793,6 +1793,34 @@
         </is>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>cordless battery lawn edger</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>$111.61</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>92.9%</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F49"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1821,6 +1821,34 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>kids art supply storage organizer rolling cart</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>$74.06</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1849,6 +1849,34 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>portable bottle warmer for travel rechargeable</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>$48.71</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>68.4%</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1877,6 +1877,34 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>tire inflator and battery jumper combo</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>$56.50</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>45.0%</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1905,6 +1905,34 @@
         </is>
       </c>
     </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>crimper hair tool lange</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>$55.44</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>61.9%</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F53"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1933,6 +1933,34 @@
         </is>
       </c>
     </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>party arch backdrop stand</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>$45.45</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>43.8%</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1961,6 +1961,34 @@
         </is>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>jump starter with air compressor and power bank</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>$58.48</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -1989,6 +1989,34 @@
         </is>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>pet water fountain large 3 gallon</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>$54.84</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>68.8%</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F56"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2017,6 +2017,34 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>cuisinart knife block set 14 piece</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>$82.33</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:F58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2045,34 @@
         </is>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>wooden wine racks for storage</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>$57.93</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F58"/>
+  <dimension ref="A1:F59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2073,6 +2073,34 @@
         </is>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>jewelry organizer wall mirror</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>$46.31</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>61.1%</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2101,6 +2101,34 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>guitar stands floor 5</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>$52.47</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>58.3%</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F60"/>
+  <dimension ref="A1:F61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2129,6 +2129,34 @@
         </is>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>lighting accessories 2024 polaris rzr xp 1000 premium 4 seater</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>$86.36</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>79.2%</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F61"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2157,6 +2157,34 @@
         </is>
       </c>
     </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>jump starter with air compressor 8000a</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>$63.41</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>76.9%</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F62"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2185,6 +2185,34 @@
         </is>
       </c>
     </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>garden cart wheels and axle</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>$51.76</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2213,6 +2213,34 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>raised garden bed with legs and trellis</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>$68.97</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>62.7%</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2241,6 +2241,34 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>anker charging station usb c</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>$57.33</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F65"/>
+  <dimension ref="A1:F66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2269,6 +2269,34 @@
         </is>
       </c>
     </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>backdrop stand for parties curtain</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>$54.98</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F66"/>
+  <dimension ref="A1:F67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2297,6 +2297,34 @@
         </is>
       </c>
     </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>car cup holder tray table tesla</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>$54.63</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>67.2%</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F67"/>
+  <dimension ref="A1:F68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2325,6 +2325,34 @@
         </is>
       </c>
     </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>baby gym activity center climbing foam</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>$86.65</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>34</v>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>75.6%</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F68"/>
+  <dimension ref="A1:F69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2353,6 +2353,34 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>indoor compost bin kitchen odorless electric</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>$304.06</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>45</v>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>83.3%</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F69"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2381,6 +2381,34 @@
         </is>
       </c>
     </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>hp tuners pro link cable</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>$43.54</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:F71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2409,6 +2409,34 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>trellis for raised garden bed metal</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>$69.99</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>37</v>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>61.7%</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F71"/>
+  <dimension ref="A1:F72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2437,6 +2437,34 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>acupressure mat</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>$43.74</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>46.2%</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F72"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2465,6 +2465,34 @@
         </is>
       </c>
     </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>beaba baby food maker glass replacement</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>$126.81</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>81.8%</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2493,6 +2493,34 @@
         </is>
       </c>
     </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>pruning shears heavy duty electric</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>$57.48</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2521,6 +2521,34 @@
         </is>
       </c>
     </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>speaker stand wooden</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>$82.30</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>62.5%</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F75"/>
+  <dimension ref="A1:F76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2549,6 +2549,34 @@
         </is>
       </c>
     </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>round raised garden beds outdoor</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>$55.98</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>28</v>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>49.1%</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F76"/>
+  <dimension ref="A1:F77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2577,6 +2577,34 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>monitor arms for 2 monitors 27 inch</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>$61.26</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F77"/>
+  <dimension ref="A1:F78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2605,6 +2605,34 @@
         </is>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>tall outdoor planters 36 inch</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>$118.17</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>78.6%</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F78"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2633,6 +2633,34 @@
         </is>
       </c>
     </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>garden trellis arch</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="n">
+        <v>47</v>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>$47.34</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>70.2%</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:F80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2661,6 +2661,34 @@
         </is>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>3 in 1 charging station apple 25w</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>$73.12</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>81.2%</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F80"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2689,6 +2689,34 @@
         </is>
       </c>
     </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>momcozy portable bottle warmer</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>$57.44</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>70.0%</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F81"/>
+  <dimension ref="A1:F82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2717,6 +2717,34 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>raised garden bed with trellis</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="n">
+        <v>56</v>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>$77.59</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>57.1%</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F82"/>
+  <dimension ref="A1:F83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2745,6 +2745,34 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>tylenol pm extra strength sleep aid liquid</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>$49.99</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2773,6 +2773,34 @@
         </is>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>salad spinner large commercial</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>$119.23</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>92.9%</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F84"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2801,6 +2801,34 @@
         </is>
       </c>
     </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>lawn edgers battery powered makita</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>$106.30</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>81.8%</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2829,6 +2829,34 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>monitor arm wall mount long</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>$59.43</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>55.6%</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F86"/>
+  <dimension ref="A1:F87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2857,6 +2857,34 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>parking sensors for cars front and rear</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>$52.66</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>45.5%</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F87"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2885,6 +2885,34 @@
         </is>
       </c>
     </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>hercules guitar stand carry bag</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>$47.96</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>47.4%</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F88"/>
+  <dimension ref="A1:F89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2913,6 +2913,34 @@
         </is>
       </c>
     </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>chainsaw safety gear stihl</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>$61.06</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>78.6%</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F89"/>
+  <dimension ref="A1:F90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2941,6 +2941,34 @@
         </is>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>garden fence tall wood</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>$40.38</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F90"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2969,6 +2969,34 @@
         </is>
       </c>
     </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>garage pegboard organizer white</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>$52.20</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>40.9%</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F91"/>
+  <dimension ref="A1:F92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -2997,6 +2997,34 @@
         </is>
       </c>
     </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>raised garden bed with trellis on wheels</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="n">
+        <v>59</v>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>$76.77</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>39</v>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>66.1%</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F92"/>
+  <dimension ref="A1:F93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3025,6 +3025,34 @@
         </is>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>backdrop stand for parties heavy duty</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>$63.10</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>56.2%</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F93"/>
+  <dimension ref="A1:F94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3053,6 +3053,34 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>car jump starter battery pack</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="n">
+        <v>44</v>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>$90.42</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>52.3%</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3081,6 +3081,34 @@
         </is>
       </c>
     </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>pet gate outdoor deck freestanding</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>$87.42</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3109,6 +3109,34 @@
         </is>
       </c>
     </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>pet gate tall wide</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>$100.00</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3137,6 +3137,34 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>compost bin outdoor tumbler</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>$79.73</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>100.0%</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F97"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3165,6 +3165,34 @@
         </is>
       </c>
     </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>canon r8 battery grip cage</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>$81.75</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F98"/>
+  <dimension ref="A1:F99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3193,6 +3193,34 @@
         </is>
       </c>
     </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>monitor arms for 2 monitors 34 inch curved</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>$98.18</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F99"/>
+  <dimension ref="A1:F100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3221,6 +3221,34 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>windsor newton watercolor set tubes</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>$71.52</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F100"/>
+  <dimension ref="A1:F101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3249,6 +3249,34 @@
         </is>
       </c>
     </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>epicka universal travel adapter voltage converter</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>$35.04</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>60.0%</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F101"/>
+  <dimension ref="A1:F102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3277,6 +3277,34 @@
         </is>
       </c>
     </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>lawn edgers battery powered dewalt</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>$101.06</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>89.5%</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F102"/>
+  <dimension ref="A1:F103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3305,6 +3305,34 @@
         </is>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>battery grip sony a7iv</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>$58.97</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>63.6%</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F103"/>
+  <dimension ref="A1:F104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3333,6 +3333,34 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>over toilet bathroom organizer wood</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>$64.45</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>78.6%</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F104"/>
+  <dimension ref="A1:F105"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3361,6 +3361,34 @@
         </is>
       </c>
     </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>car jump starter with air compressor</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>$64.52</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>77.8%</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F105"/>
+  <dimension ref="A1:F106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3389,6 +3389,34 @@
         </is>
       </c>
     </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>windsor newton watercolor set 12</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>$57.46</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>42.9%</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F106"/>
+  <dimension ref="A1:F107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3417,6 +3417,34 @@
         </is>
       </c>
     </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>cleaning caddy bag with wheels</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="n">
+        <v>60</v>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>$58.10</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>55.0%</t>
+        </is>
+      </c>
+      <c r="F107" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F107"/>
+  <dimension ref="A1:F108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3445,6 +3445,34 @@
         </is>
       </c>
     </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>tulip crochet hook set purple</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>$49.66</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>52.6%</t>
+        </is>
+      </c>
+      <c r="F108" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F108"/>
+  <dimension ref="A1:F109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3473,6 +3473,34 @@
         </is>
       </c>
     </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>ego lawn edger me0823</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>$90.39</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F109" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3501,6 +3501,34 @@
         </is>
       </c>
     </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>cleaning caddy with wheels pink</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>$60.16</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>92.9%</t>
+        </is>
+      </c>
+      <c r="F110" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F110"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3529,6 +3529,34 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>tire inflator and battery jumper dual power</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>$63.57</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>71.4%</t>
+        </is>
+      </c>
+      <c r="F111" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F111"/>
+  <dimension ref="A1:F112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3557,6 +3557,34 @@
         </is>
       </c>
     </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>battery grip for canon r6 mark iii</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>$109.47</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>85.7%</t>
+        </is>
+      </c>
+      <c r="F112" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F112"/>
+  <dimension ref="A1:F113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3585,6 +3585,34 @@
         </is>
       </c>
     </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>ricou browning</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="n">
+        <v>35</v>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>$228.10</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>32</v>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>91.4%</t>
+        </is>
+      </c>
+      <c r="F113" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F113"/>
+  <dimension ref="A1:F114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3613,6 +3613,34 @@
         </is>
       </c>
     </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>lexa doig</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>$40.91</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F114" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F114"/>
+  <dimension ref="A1:F115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3641,6 +3641,34 @@
         </is>
       </c>
     </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>susan ursitti</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>$26.48</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F115" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F115"/>
+  <dimension ref="A1:F116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3669,6 +3669,34 @@
         </is>
       </c>
     </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>kirti kulhari</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>$41.12</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>66.7%</t>
+        </is>
+      </c>
+      <c r="F116" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F116"/>
+  <dimension ref="A1:F117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3697,6 +3697,34 @@
         </is>
       </c>
     </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>miguel puga</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>$33.16</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>40.0%</t>
+        </is>
+      </c>
+      <c r="F117" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F117"/>
+  <dimension ref="A1:F118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3725,6 +3725,34 @@
         </is>
       </c>
     </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>friz freleng</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>$380.04</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>54.5%</t>
+        </is>
+      </c>
+      <c r="F118" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F118"/>
+  <dimension ref="A1:F119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3753,6 +3753,34 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>john cena</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>$41.34</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/amazon_niche_rapor_2026-04-06.xlsx
+++ b/output/amazon_niche_rapor_2026-04-06.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F119"/>
+  <dimension ref="A1:F120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -3781,6 +3781,34 @@
         </is>
       </c>
     </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>zoltan mucsi</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>$55.13</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>50.0%</t>
+        </is>
+      </c>
+      <c r="F120" s="2" t="inlineStr">
+        <is>
+          <t>✅ GİRİLEBİLİR</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
